--- a/assets/constructions/examples/ctd_mi_cap.xlsx
+++ b/assets/constructions/examples/ctd_mi_cap.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y6"/>
+  <dimension ref="A1:AC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,11 +554,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>12393051200</t>
+          <t>12393060800</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -568,12 +588,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>M390</t>
+          <t>M300</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -581,22 +601,22 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>21.2</v>
+        <v>28.8</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2</v>
+        <v>0.65</v>
       </c>
       <c r="N2" t="n">
-        <v>21.2</v>
+        <v>28.8</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -605,7 +625,7 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
@@ -616,22 +636,22 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>WIDIA_CAP_D50+WIDIA_SD1204H</t>
+          <t>WIDIA_CAP_D80+WIDIA_XP1604H</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>WIDIA_SD1204H</t>
+          <t>WIDIA_XP1604H</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>WID_CAP_D50_SD12-WID_SD1204_H</t>
+          <t>WID_CAP_D80_XP16-WID_XP1604_H</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>WID_123969_2938</t>
+          <t>WID_123930_3449</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -639,11 +659,17 @@
           <t>2017 / WIDIA основной каталог EN</t>
         </is>
       </c>
+      <c r="Z2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>12393060800</t>
+          <t>12393051200</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -653,12 +679,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>M300</t>
+          <t>M390</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -666,31 +692,31 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>28.8</v>
+        <v>21.2</v>
       </c>
       <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
         <v>4</v>
-      </c>
-      <c r="K3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L3" t="n">
-        <v>4</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="N3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2</v>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
@@ -701,22 +727,22 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>WIDIA_CAP_D80+WIDIA_XP1604H</t>
+          <t>WIDIA_CAP_D50+WIDIA_SD1204H</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>WIDIA_XP1604H</t>
+          <t>WIDIA_SD1204H</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>WID_CAP_D80_XP16-WID_XP1604_H</t>
+          <t>WID_CAP_D50_SD12-WID_SD1204_H</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>WID_123930_3449</t>
+          <t>WID_123969_2938</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -724,11 +750,17 @@
           <t>2017 / WIDIA основной каталог EN</t>
         </is>
       </c>
+      <c r="Z3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>12393051800</t>
+          <t>12393060400</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -738,12 +770,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>M390</t>
+          <t>M300</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -751,22 +783,22 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>21.2</v>
+        <v>28.8</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="N4" t="n">
-        <v>21.2</v>
+        <v>28.8</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -775,7 +807,7 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
@@ -786,22 +818,22 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>WIDIA_CAP_D80+WIDIA_SD1204H</t>
+          <t>WIDIA_CAP_D63+WIDIA_XP1604H</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>WIDIA_SD1204H</t>
+          <t>WIDIA_XP1604H</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>WID_CAP_D80_SD12-WID_SD1204_H</t>
+          <t>WID_CAP_D63_XP16-WID_XP1604_H</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>WID_123969_2938</t>
+          <t>WID_123930_3449</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -809,11 +841,17 @@
           <t>2017 / WIDIA основной каталог EN</t>
         </is>
       </c>
+      <c r="Z4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12393051400</t>
+          <t>12393060200</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -823,12 +861,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>M390</t>
+          <t>M300</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -836,22 +874,22 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>21.2</v>
+        <v>28.8</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M5" t="n">
         <v>0.3</v>
       </c>
       <c r="N5" t="n">
-        <v>21.2</v>
+        <v>28.8</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -860,7 +898,7 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
@@ -871,22 +909,22 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>WIDIA_CAP_D63+WIDIA_SD1204H</t>
+          <t>WIDIA_CAP_D50+WIDIA_XP1604H</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>WIDIA_SD1204H</t>
+          <t>WIDIA_XP1604H</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>WID_CAP_D63_SD12-WID_SD1204_H</t>
+          <t>WID_CAP_D50_XP16-WID_XP1604_H</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>WID_123969_2938</t>
+          <t>WID_123930_3449</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -894,11 +932,17 @@
           <t>2017 / WIDIA основной каталог EN</t>
         </is>
       </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12393060400</t>
+          <t>12393051800</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -908,12 +952,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>M300</t>
+          <t>M390</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -921,22 +965,22 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>28.8</v>
+        <v>21.2</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M6" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="N6" t="n">
-        <v>28.8</v>
+        <v>21.2</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -945,7 +989,7 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
@@ -956,22 +1000,22 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>WIDIA_CAP_D63+WIDIA_XP1604H</t>
+          <t>WIDIA_CAP_D80+WIDIA_SD1204H</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>WIDIA_XP1604H</t>
+          <t>WIDIA_SD1204H</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>WID_CAP_D63_XP16-WID_XP1604_H</t>
+          <t>WID_CAP_D80_SD12-WID_SD1204_H</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>WID_123930_3449</t>
+          <t>WID_123969_2938</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -979,6 +1023,12 @@
           <t>2017 / WIDIA основной каталог EN</t>
         </is>
       </c>
+      <c r="Z6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
